--- a/artfynd/A 12817-2026 artfynd.xlsx
+++ b/artfynd/A 12817-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,53 +675,48 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>62400423</v>
+        <v>132654204</v>
       </c>
       <c r="B2" t="n">
-        <v>103813</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96410</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220785</v>
+        <v>2812</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Kransmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Hylocomiadelphus triquetrus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Hedw.) Ochyra &amp; Stebel</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Bispberg, Dlr</t>
+          <t>Bispbergs gruva, Bispbergs gruva, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>544068.3789713542</v>
+        <v>543985</v>
       </c>
       <c r="R2" t="n">
-        <v>6691769.305123988</v>
+        <v>6691850</v>
       </c>
       <c r="S2" t="n">
-        <v>100</v>
+        <v>25</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -745,27 +740,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>1968-01-01</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>1968-12-31</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Dalafloran [260]   enstaka</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -777,39 +757,25 @@
       <c r="AG2" t="b">
         <v>0</v>
       </c>
-      <c r="AI2" t="inlineStr">
-        <is>
-          <t>hage</t>
-        </is>
-      </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Inge Palmqvist</t>
+          <t>Patric Engfeldt</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Elis Dahlgren</t>
-        </is>
-      </c>
-      <c r="AY2" t="inlineStr">
-        <is>
-          <t>Dalaflorans databas</t>
-        </is>
-      </c>
+          <t>Patric Engfeldt</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
         <v>109429357</v>
       </c>
       <c r="B3" t="n">
-        <v>56632</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58238</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -853,10 +819,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>544050.6444719379</v>
+        <v>544051</v>
       </c>
       <c r="R3" t="n">
-        <v>6691923.971428091</v>
+        <v>6691924</v>
       </c>
       <c r="S3" t="n">
         <v>50</v>
@@ -886,19 +852,9 @@
           <t>2023-05-22</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2023-05-22</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -922,6 +878,117 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>62400423</v>
+      </c>
+      <c r="B4" t="n">
+        <v>106813</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>220785</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Ask</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Bispberg, Dlr</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>544068</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6691769</v>
+      </c>
+      <c r="S4" t="n">
+        <v>100</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Säter</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Säter</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>1968-01-01</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>1968-12-31</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Dalafloran [260]   enstaka</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>hage</t>
+        </is>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Inge Palmqvist</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Elis Dahlgren</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr">
+        <is>
+          <t>Dalaflorans databas</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 12817-2026 artfynd.xlsx
+++ b/artfynd/A 12817-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AZ4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132654204</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -878,6 +888,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109429357</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -989,8 +1004,18 @@
           <t>Dalaflorans databas</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/62400423</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>